--- a/data/ams_weekly_data/Nexlev/ads_report_week31.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week31.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -932,13 +921,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44981.36</v>
+        <v>44978.98</v>
       </c>
       <c r="E18" t="n">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="F18" t="n">
-        <v>435983</v>
+        <v>435982</v>
       </c>
       <c r="G18" t="n">
         <v>219790.65</v>
@@ -1389,10 +1378,10 @@
         <v>18960</v>
       </c>
       <c r="G34" t="n">
-        <v>18642.37</v>
+        <v>27963.56</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1806,7 +1795,7 @@
         <v>242</v>
       </c>
       <c r="F49" t="n">
-        <v>213089</v>
+        <v>213087</v>
       </c>
       <c r="G49" t="n">
         <v>7285.6</v>
@@ -2422,7 +2411,7 @@
         <v>1049</v>
       </c>
       <c r="F71" t="n">
-        <v>153081</v>
+        <v>153080</v>
       </c>
       <c r="G71" t="n">
         <v>24339.84</v>
@@ -2478,7 +2467,7 @@
         <v>555</v>
       </c>
       <c r="F73" t="n">
-        <v>84415</v>
+        <v>84412</v>
       </c>
       <c r="G73" t="n">
         <v>21487.32</v>
@@ -2593,10 +2582,10 @@
         <v>127277</v>
       </c>
       <c r="G77" t="n">
-        <v>102327.96</v>
+        <v>81990.68000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -2674,7 +2663,7 @@
         <v>104</v>
       </c>
       <c r="F80" t="n">
-        <v>51644</v>
+        <v>51643</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2845,10 +2834,10 @@
         <v>57059</v>
       </c>
       <c r="G86" t="n">
-        <v>50843.2</v>
+        <v>71180.48</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -3094,7 +3083,7 @@
         <v>172</v>
       </c>
       <c r="F95" t="n">
-        <v>44337</v>
+        <v>44336</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3629,10 +3618,10 @@
         <v>78338</v>
       </c>
       <c r="G114" t="n">
-        <v>15335.59</v>
+        <v>13556.78</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -3990,7 +3979,7 @@
         <v>17</v>
       </c>
       <c r="F127" t="n">
-        <v>5528</v>
+        <v>5527</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4242,7 +4231,7 @@
         <v>1076</v>
       </c>
       <c r="F136" t="n">
-        <v>95616</v>
+        <v>95614</v>
       </c>
       <c r="G136" t="n">
         <v>89038.09999999999</v>
@@ -4942,7 +4931,7 @@
         <v>97</v>
       </c>
       <c r="F161" t="n">
-        <v>35544</v>
+        <v>35543</v>
       </c>
       <c r="G161" t="n">
         <v>3727.12</v>
@@ -4973,10 +4962,10 @@
         <v>25880</v>
       </c>
       <c r="G162" t="n">
-        <v>951.4299999999999</v>
+        <v>1902.86</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -5166,7 +5155,7 @@
         <v>60</v>
       </c>
       <c r="F169" t="n">
-        <v>31805</v>
+        <v>31804</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5278,7 +5267,7 @@
         <v>307</v>
       </c>
       <c r="F173" t="n">
-        <v>25084</v>
+        <v>25083</v>
       </c>
       <c r="G173" t="n">
         <v>6438.98</v>
@@ -5306,7 +5295,7 @@
         <v>542</v>
       </c>
       <c r="F174" t="n">
-        <v>61485</v>
+        <v>61481</v>
       </c>
       <c r="G174" t="n">
         <v>16772.01</v>
@@ -5362,7 +5351,7 @@
         <v>628</v>
       </c>
       <c r="F176" t="n">
-        <v>38426</v>
+        <v>38424</v>
       </c>
       <c r="G176" t="n">
         <v>15504.24</v>
@@ -5474,7 +5463,7 @@
         <v>463</v>
       </c>
       <c r="F180" t="n">
-        <v>65626</v>
+        <v>65625</v>
       </c>
       <c r="G180" t="n">
         <v>17791.5</v>
@@ -5638,42 +5627,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -6965,6 +6954,1453 @@
       </c>
       <c r="H47" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="E2" t="n">
+        <v>187</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3033.35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14063.54</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5405</v>
+      </c>
+      <c r="E3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" t="n">
+        <v>440.4299999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2796.19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17744</v>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>932.8933333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17744</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>932.8933333333333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17744</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>932.8933333333333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7259</v>
+      </c>
+      <c r="E7" t="n">
+        <v>223</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2780.36</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33892.36</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6857</v>
+      </c>
+      <c r="E8" t="n">
+        <v>355</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4860.51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16521.17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5257</v>
+      </c>
+      <c r="E9" t="n">
+        <v>150</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1880.76</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13385.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6865</v>
+      </c>
+      <c r="E10" t="n">
+        <v>119</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1563.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16738</v>
+      </c>
+      <c r="E11" t="n">
+        <v>153</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2737.23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1614</v>
+      </c>
+      <c r="E12" t="n">
+        <v>75</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3005.84</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2965.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8767</v>
+      </c>
+      <c r="E13" t="n">
+        <v>104</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1069.36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- Exact 01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>155.79</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>25725</v>
+      </c>
+      <c r="E15" t="n">
+        <v>280</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3967.28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-Exact- SBV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11138</v>
+      </c>
+      <c r="E16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F16" t="n">
+        <v>476.77</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01-SBV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13525</v>
+      </c>
+      <c r="E17" t="n">
+        <v>207</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3346.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10168.64</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-Phrase- SBV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16923</v>
+      </c>
+      <c r="E18" t="n">
+        <v>120</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1897.91</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-SBV-PT01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>555.4699999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11589</v>
+      </c>
+      <c r="E20" t="n">
+        <v>159</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1535.571517896719</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18827.83061266134</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>17385</v>
+      </c>
+      <c r="E21" t="n">
+        <v>238</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2303.552112976509</v>
+      </c>
+      <c r="G21" t="n">
+        <v>28244.13482868266</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10140</v>
+      </c>
+      <c r="E22" t="n">
+        <v>139</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1343.576369126772</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16473.754558656</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8471</v>
+      </c>
+      <c r="E23" t="n">
+        <v>91</v>
+      </c>
+      <c r="F23" t="n">
+        <v>982.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5585</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>835.1899999999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3992</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>576.6600000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F26" t="n">
+        <v>305.38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1359</v>
+      </c>
+      <c r="E27" t="n">
+        <v>88</v>
+      </c>
+      <c r="F27" t="n">
+        <v>671.8399999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6777.96</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>792</v>
+      </c>
+      <c r="E28" t="n">
+        <v>56</v>
+      </c>
+      <c r="F28" t="n">
+        <v>420.76</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>19086</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1171</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11131.45322759076</v>
+      </c>
+      <c r="G29" t="n">
+        <v>125587.2989001381</v>
+      </c>
+      <c r="H29" t="n">
+        <v>38</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7808</v>
+      </c>
+      <c r="E30" t="n">
+        <v>479</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4554.161514707456</v>
+      </c>
+      <c r="G30" t="n">
+        <v>51380.96811739107</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12145</v>
+      </c>
+      <c r="E31" t="n">
+        <v>745</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7083.395257701782</v>
+      </c>
+      <c r="G31" t="n">
+        <v>79916.29298247087</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>8864</v>
+      </c>
+      <c r="E32" t="n">
+        <v>312</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4297.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6777.96</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>22850</v>
+      </c>
+      <c r="E33" t="n">
+        <v>458</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5409.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16266.94</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>650</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" t="n">
+        <v>214.15</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13720</v>
+      </c>
+      <c r="E35" t="n">
+        <v>182</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1809.74</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5422.030000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12044</v>
+      </c>
+      <c r="E37" t="n">
+        <v>283</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2849.04</v>
+      </c>
+      <c r="G37" t="n">
+        <v>11522.02</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11797</v>
+      </c>
+      <c r="E38" t="n">
+        <v>402</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5797.69</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20756.75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>28472</v>
+      </c>
+      <c r="E39" t="n">
+        <v>520</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6940.58</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22875.41</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2361</v>
+      </c>
+      <c r="E40" t="n">
+        <v>35</v>
+      </c>
+      <c r="F40" t="n">
+        <v>575.37</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>17788</v>
+      </c>
+      <c r="E41" t="n">
+        <v>215</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2492.21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4490.68</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4863</v>
+      </c>
+      <c r="E42" t="n">
+        <v>112</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1870.21</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>228</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>172.67</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ams_weekly_data/Nexlev/ads_report_week31.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week31.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -921,13 +933,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44978.98</v>
+        <v>44981.36</v>
       </c>
       <c r="E18" t="n">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="F18" t="n">
-        <v>435982</v>
+        <v>435983</v>
       </c>
       <c r="G18" t="n">
         <v>219790.65</v>
@@ -1378,10 +1390,10 @@
         <v>18960</v>
       </c>
       <c r="G34" t="n">
-        <v>27963.56</v>
+        <v>18642.37</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1795,7 +1807,7 @@
         <v>242</v>
       </c>
       <c r="F49" t="n">
-        <v>213087</v>
+        <v>213089</v>
       </c>
       <c r="G49" t="n">
         <v>7285.6</v>
@@ -2411,7 +2423,7 @@
         <v>1049</v>
       </c>
       <c r="F71" t="n">
-        <v>153080</v>
+        <v>153081</v>
       </c>
       <c r="G71" t="n">
         <v>24339.84</v>
@@ -2467,7 +2479,7 @@
         <v>555</v>
       </c>
       <c r="F73" t="n">
-        <v>84412</v>
+        <v>84415</v>
       </c>
       <c r="G73" t="n">
         <v>21487.32</v>
@@ -2582,10 +2594,10 @@
         <v>127277</v>
       </c>
       <c r="G77" t="n">
-        <v>81990.68000000001</v>
+        <v>102327.96</v>
       </c>
       <c r="H77" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -2663,7 +2675,7 @@
         <v>104</v>
       </c>
       <c r="F80" t="n">
-        <v>51643</v>
+        <v>51644</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2834,10 +2846,10 @@
         <v>57059</v>
       </c>
       <c r="G86" t="n">
-        <v>71180.48</v>
+        <v>50843.2</v>
       </c>
       <c r="H86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -3083,7 +3095,7 @@
         <v>172</v>
       </c>
       <c r="F95" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3618,10 +3630,10 @@
         <v>78338</v>
       </c>
       <c r="G114" t="n">
-        <v>13556.78</v>
+        <v>15335.59</v>
       </c>
       <c r="H114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -3979,7 +3991,7 @@
         <v>17</v>
       </c>
       <c r="F127" t="n">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4231,7 +4243,7 @@
         <v>1076</v>
       </c>
       <c r="F136" t="n">
-        <v>95614</v>
+        <v>95616</v>
       </c>
       <c r="G136" t="n">
         <v>89038.09999999999</v>
@@ -4931,7 +4943,7 @@
         <v>97</v>
       </c>
       <c r="F161" t="n">
-        <v>35543</v>
+        <v>35544</v>
       </c>
       <c r="G161" t="n">
         <v>3727.12</v>
@@ -4962,10 +4974,10 @@
         <v>25880</v>
       </c>
       <c r="G162" t="n">
-        <v>1902.86</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -5155,7 +5167,7 @@
         <v>60</v>
       </c>
       <c r="F169" t="n">
-        <v>31804</v>
+        <v>31805</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5267,7 +5279,7 @@
         <v>307</v>
       </c>
       <c r="F173" t="n">
-        <v>25083</v>
+        <v>25084</v>
       </c>
       <c r="G173" t="n">
         <v>6438.98</v>
@@ -5295,7 +5307,7 @@
         <v>542</v>
       </c>
       <c r="F174" t="n">
-        <v>61481</v>
+        <v>61485</v>
       </c>
       <c r="G174" t="n">
         <v>16772.01</v>
@@ -5351,7 +5363,7 @@
         <v>628</v>
       </c>
       <c r="F176" t="n">
-        <v>38424</v>
+        <v>38426</v>
       </c>
       <c r="G176" t="n">
         <v>15504.24</v>
@@ -5463,7 +5475,7 @@
         <v>463</v>
       </c>
       <c r="F180" t="n">
-        <v>65625</v>
+        <v>65626</v>
       </c>
       <c r="G180" t="n">
         <v>17791.5</v>
@@ -5627,42 +5639,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -6971,47 +6983,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
